--- a/paper_tables/Table_5_Actual_vs_Predicted_young_modulus.xlsx
+++ b/paper_tables/Table_5_Actual_vs_Predicted_young_modulus.xlsx
@@ -89,16 +89,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,136 +465,2807 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Actual young_modulus</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Predicted young_modulus</t>
+          <t>Chemical Family</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Abs Error</t>
+          <t>DFT Actual [GPa]</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Rel Error (%)</t>
+          <t>CGCNN Predicted [GPa]</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Absolute Error |Δ|</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1035.127</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1023.184</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>11.943</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>1.154</v>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Carbides</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1035.126754244769</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1036.039907838599</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>NbC</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Carbides</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>481.8500481520399</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>484.7692426461933</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2.919</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>FeOF</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
-        <v>230.941</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>256.652</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>25.711</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>11.133</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>NbC</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>481.85</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>489.912</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>8.061</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1.673</v>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>230.94101797886</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>241.4022848767369</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>10.461</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Rb2F</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>11.81843528126707</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>10.2016208727253</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1.617</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>CuMoO4</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>153.4984963900112</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>158.197220336822</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>4.699</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>NbF3</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>116.506</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>98.842</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>17.665</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>15.162</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Rb2F</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>11.818</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>12.531</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>6.033</v>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>116.5064056961066</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>113.6381636232273</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2.868</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>HoBrO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>67.25049000169943</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>69.87816683566626</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2.628</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Mn2F7</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>59.23611887423736</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>59.08704749630527</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.149</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>MnF4</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>79.49197749196142</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>76.2989106882623</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3.193</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>YMg5</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Intermetallics/Alloys</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>44.8953006219765</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>45.90234640435155</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1.007</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Semimetals</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>154.7226929773651</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>156.2277485323067</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1.505</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>TmBrO</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>65.88415357652862</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>67.6924478129565</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1.808</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>HgF2</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>54.9010543836625</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>57.86450361069024</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2.963</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>As2Pt</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>213.4310672529432</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>214.4789858500919</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1.048</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Mg2SiO4</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>291.4956519491708</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>294.3438451290706</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2.848</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>BaV4O8</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>24.32132842044022</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>16.26666435543494</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>8.055</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>SmZnPO</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>138.0712166172107</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>135.2670842482993</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2.804</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>UBrO2</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>107.5971651495449</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>107.8061296162475</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.209</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>NiSb2</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>112.5300545869587</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>117.9593449362463</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>5.429</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Na2I</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>4.140239441303624</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>5.426633699565697</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1.286</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>GaTeCl</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>4.437993506493505</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2.693336486781577</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1.745</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>P2Pt</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>296.0358991286392</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>300.8359352317904</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>GaTe</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>40.92943264659271</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>38.54052316845127</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2.389</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>NaMgSb</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>44.48016356028909</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>44.13431582415018</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.346</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>TiTl2F6</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>36.76292805755396</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>43.15519717350831</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>6.392</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>VOF</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>121.9838148344288</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>118.2382147554598</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>3.746</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>YClO</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>109.9038589256647</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>115.6568923073975</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>5.753</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>InTeI</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>20.76208169543668</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>23.42002843355207</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2.658</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>CaPbI4</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>20.7074447592068</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>17.41825957946817</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>3.289</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Sr2FeBrO3</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>90.28281663245332</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>94.71226742559794</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>4.429</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>TePb</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>72.54182136602451</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>80.62327089495436</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>8.081</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>TlPd2Se3</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>49.81194499017683</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>56.77571839616211</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>6.964</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>NbI2O</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>57.54422908486862</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>58.49466247164596</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>PdCl2</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>33.41684420772304</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>38.67867436472856</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>5.262</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>SnO</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>78.99240225371349</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>79.74143719067224</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Se</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>48.69793356003138</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>49.99919245761656</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1.301</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>VSe3</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>20.55598869169153</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>32.16653002158721</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>11.611</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Bi2Pt</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>24.61764705882353</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>22.26477693663382</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2.353</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Hg</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Intermetallics/Alloys</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>13.39906432748538</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>16.30374314262022</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>2.905</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>TeO3</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Oxychalcogenides</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>114.2745931170756</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>122.3501035029056</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>8.076000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>UBr4</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>23.00976342806129</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>16.89041079365165</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>6.119</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>HfS2</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>82.43422776911076</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>88.65394322877964</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>P2Pt</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>296.0358991286392</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>299.3940401757617</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>3.358</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>AgSb2F12</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>27.25185063224447</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>33.14072603752832</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>5.889</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>ZrSe3</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>59.42226037817866</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>59.55161208138534</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Bi2Pt</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>24.61764705882353</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>22.28984903337185</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>2.328</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>SnSe2</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>52.59541071828986</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>49.00307311786681</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>3.592</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>TiBr3</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>35.80722654754307</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>38.84391426229279</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>3.037</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>ScAs2</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>90.36313139020297</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>91.41709768661731</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>1.054</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Ag2Se</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>41.32551542623192</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>37.19158166705302</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>4.134</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>NaMgSb</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>44.48016356028909</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>41.98051652406794</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Mg(ReO4)2</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>31.43283582089552</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>26.94024263757096</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>4.493</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Nb(SCl)2</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>55.47679938744258</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>53.14754854177981</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>2.329</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>176.8511404647014</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>180.8544790450068</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>4.003</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>AlPd5I2</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>32.05479452054794</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>38.59502466757759</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>ZrBr3</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>9.473684210526317</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>15.8135527318216</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>FeC2O6</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>29.73913043478262</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>27.58476163729697</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>2.154</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>CrO3</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>30.75748328794256</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>30.68358025561518</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0.074</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Sb2TeSe2</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>57.48517171413542</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>54.72762260695568</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>2.758</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>B2S</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>27.49321692411014</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>38.4716744983063</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>10.978</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>SbCl5</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>13.74247085656361</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>12.94620833284039</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0.796</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Ga</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Intermetallics/Alloys</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>18.47119771863118</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>12.42117041897693</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Li2CeAs2</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>81.95560656941967</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>79.38724824754703</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>2.568</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Ca(HO)2</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>65.79679190936439</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>65.04476054793854</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0.752</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>NaSbO2</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>87.16158234618281</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>84.2917524170519</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>SnF4</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>33.34680745341615</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>28.82817400303184</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>4.519</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Al2S3</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>60.10083327556326</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>65.08999938818634</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>4.989</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>AuS2</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>55.96783801342669</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>67.01668864302572</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>11.049</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Cu2Te</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>36.44738797993916</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>37.31990467806518</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.873</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Te2W</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>74.30636252177842</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>72.10388503044642</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>2.202</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>AsC</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>54.09948476161738</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>56.38221790160022</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>2.283</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>TiGeO3</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>228.2788958336533</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>227.010865093781</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>1.268</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>CrSe</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>52.60702040816327</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>47.55477131113293</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>5.052</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>NbS2</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>79.23144104803494</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>86.33951570382314</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>7.108</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>SiP2</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>60.33420698392589</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>65.68197671444227</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>5.348</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>VPbClO3</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>65.98706128461991</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>63.8514195725725</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>2.136</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>TaS2</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>102.0348522784176</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>112.3798938347043</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>10.345</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Hg2ClO</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>24.62248604001861</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>25.3640813761768</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0.742</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>KAuSe2</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>36.54535081573415</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>37.53152729022188</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>0.986</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>CoI2</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>34.12960196350443</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>33.97351997026392</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>NiS2</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>27.16293359762141</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>23.70784455465283</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>3.455</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>ClF</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>21.56436755530346</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>20.17936549801496</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>1.385</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Ag2SO4</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Oxychalcogenides</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>26.09550081286127</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>31.44607520284525</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>5.351</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>ZrO2</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>128.8269994339526</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>127.4357248783437</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>1.391</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>SbClO</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>96.90734978229318</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>94.90258843598971</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>2.005</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Au2S</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>14.72816837115393</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>16.84953837489275</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>2.121</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>TmAgP2Se6</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>37.35157585835859</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>30.53072734087105</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>6.821</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>PbIF</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>40.02406375593716</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>41.22578995234883</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>1.202</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Nb3SBr7</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>56.53763991908295</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>55.57469012006816</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0.963</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>LiBi4F20</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>59.4838888034451</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>59.61779143117595</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>0.134</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Mg2Al2Se5</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>58.86152820998512</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>58.98439563863576</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>AgBiO2</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>57.44361153582538</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>57.22102484238943</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>As2O3</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>34.63038609543355</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>30.95417557599099</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>3.676</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>PbSe</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>81.89734690553746</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>82.89694887788917</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Nb2O5</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>152.5618363592253</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>153.4463328535274</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0.884</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>VSe</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>57.79166339074524</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>55.71142459157255</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Te2SO7</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Oxychalcogenides</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>59.1757993006993</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>61.5138105657435</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>2.338</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>SiS</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>12.81503355704698</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>15.03106424508365</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>2.216</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>GaSe</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>52.26052938238721</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>59.32222241285346</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>7.062</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>BiBr3</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>15.80567441860465</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>22.4836343211212</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>6.678</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>PF5</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>18.93747570850202</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>19.37001920473645</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0.433</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>CN2</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Pnictides</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>434.2727771342113</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>427.5877554555449</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>6.685</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>HgPS3</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>39.65431443349273</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>49.3889606883673</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>9.734999999999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>VS2</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>74.65148828585876</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>72.32928700888058</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>2.322</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>SbI3</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>14.53567482241515</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>12.55688506018137</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>1.979</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>ZrS2</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>77.04602595345438</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>75.09079293000896</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>1.955</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>PI3</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>15.70970111731844</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>22.68695333498178</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>6.977</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>ErAgP2Se6</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>36.60742671009772</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>38.32827056792595</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>1.721</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>PI2</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>16.9741843617287</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>15.08334368479735</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>1.891</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>BCl3</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>13.87487323943662</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>12.24209971745816</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>1.633</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>NaHO</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>39.19587250777391</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>43.83917293538277</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>4.643</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>AgClO2</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>3.872923538230885</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>9.523826103311729</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>5.651</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>K(SbSe2)2</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Chalcogenides</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>34.167016183412</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>30.14128332342423</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>4.026</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>HfCl4</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>23.11361372440509</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>22.27269132567898</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>0.841</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>LiCr9O27</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>30.75748328794256</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>30.88491598052963</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0.127</v>
       </c>
     </row>
   </sheetData>
